--- a/assets/binomial/practice/Binomial Option Practice 5.xlsx
+++ b/assets/binomial/practice/Binomial Option Practice 5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\5 Binomial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\FIN 203\FIN 203 Fall 2020\S3 Online\assets\binomial\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F60899-0273-4468-89D5-492CF3505961}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E091031-BB0F-4C77-A2FE-A9E991F5DA4B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>u</t>
   </si>
@@ -127,6 +127,9 @@
   <si>
     <t>Optimal Decision</t>
   </si>
+  <si>
+    <t>Price an American call option</t>
+  </si>
 </sst>
 </file>
 
@@ -138,7 +141,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -149,6 +152,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -188,7 +199,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -221,6 +232,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2031,6 +2043,9 @@
       <c r="APZ12" s="8"/>
     </row>
     <row r="13" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="A13" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="C13" s="3"/>
       <c r="F13" s="1">
         <f>E9*C2</f>
